--- a/data/RDSon_vs_Tj.xlsx
+++ b/data/RDSon_vs_Tj.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\Power-MOSFET-Thermal-Reliability-Analysis\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8BA27D3F-7535-483C-A424-D3EF8E29F0B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B92DE30C-2DC1-4D64-8D91-806BAF289BA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{BD626BE4-03B3-437A-BBBD-C86995C26C44}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="6">
   <si>
     <t>Tj (°C)</t>
   </si>
@@ -108,12 +108,9 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -458,33 +455,121 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBA197A1-5494-4B42-9235-4CE3436ACECF}">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="4" width="15.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="52.2" x14ac:dyDescent="0.4">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" s="4" t="s">
+    <row r="2" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A2" s="3">
+        <v>25</v>
+      </c>
+      <c r="B2" s="3">
+        <v>1.49</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A3" s="3">
+        <v>50</v>
+      </c>
+      <c r="B3" s="3">
+        <v>1.69</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A4" s="3">
+        <v>75</v>
+      </c>
+      <c r="B4" s="3">
+        <v>1.91</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A5" s="3">
+        <v>100</v>
+      </c>
+      <c r="B5" s="3">
+        <v>2.17</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A6" s="3">
+        <v>125</v>
+      </c>
+      <c r="B6" s="3">
+        <v>2.44</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A7" s="3">
+        <v>150</v>
+      </c>
+      <c r="B7" s="3">
+        <v>2.74</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A8" s="3">
+        <v>175</v>
+      </c>
+      <c r="B8" s="3">
+        <v>3.08</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>5</v>
       </c>
     </row>
